--- a/data/conf_snap_output/conf_snap_t.xlsx
+++ b/data/conf_snap_output/conf_snap_t.xlsx
@@ -414,7 +414,7 @@
         <v>0.01</v>
       </c>
       <c r="C2">
-        <v>0.01</v>
+        <v>0.1</v>
       </c>
       <c r="D2">
         <v>1000</v>
@@ -426,16 +426,16 @@
         <v>0.05</v>
       </c>
       <c r="G2">
-        <v>0.4615384615384616</v>
+        <v>0.366120218579235</v>
       </c>
       <c r="H2">
-        <v>0.5384615384615384</v>
+        <v>0.6338797814207651</v>
       </c>
       <c r="I2">
-        <v>0.74</v>
+        <v>0.8169999999999999</v>
       </c>
       <c r="J2">
-        <v>50</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="3">
@@ -446,7 +446,7 @@
         <v>0.01</v>
       </c>
       <c r="C3">
-        <v>0.01</v>
+        <v>0.1</v>
       </c>
       <c r="D3">
         <v>1000</v>
@@ -458,16 +458,16 @@
         <v>0.05</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>0.1590909090909091</v>
       </c>
       <c r="H3">
-        <v>1</v>
+        <v>0.8409090909090909</v>
       </c>
       <c r="I3">
-        <v>0.96</v>
+        <v>0.956</v>
       </c>
       <c r="J3">
-        <v>50</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="4">
@@ -478,7 +478,7 @@
         <v>0.01</v>
       </c>
       <c r="C4">
-        <v>0.01</v>
+        <v>0.1</v>
       </c>
       <c r="D4">
         <v>1000</v>
@@ -490,16 +490,16 @@
         <v>0.05</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>0.0847457627118644</v>
       </c>
       <c r="H4">
-        <v>1</v>
+        <v>0.9152542372881356</v>
       </c>
       <c r="I4">
-        <v>0.9399999999999999</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="J4">
-        <v>50</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="5">
@@ -510,7 +510,7 @@
         <v>0.01</v>
       </c>
       <c r="C5">
-        <v>0.01</v>
+        <v>0.1</v>
       </c>
       <c r="D5">
         <v>1000</v>
@@ -522,16 +522,16 @@
         <v>0.05</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>0.1875</v>
       </c>
       <c r="H5">
-        <v>1</v>
+        <v>0.8125</v>
       </c>
       <c r="I5">
-        <v>0.92</v>
+        <v>0.952</v>
       </c>
       <c r="J5">
-        <v>50</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="6">
@@ -542,7 +542,7 @@
         <v>0.01</v>
       </c>
       <c r="C6">
-        <v>0.01</v>
+        <v>0.1</v>
       </c>
       <c r="D6">
         <v>1000</v>
@@ -554,16 +554,16 @@
         <v>0.05</v>
       </c>
       <c r="G6">
-        <v>0.5</v>
+        <v>0.1052631578947368</v>
       </c>
       <c r="H6">
-        <v>0.5</v>
+        <v>0.8947368421052632</v>
       </c>
       <c r="I6">
-        <v>0.96</v>
+        <v>0.962</v>
       </c>
       <c r="J6">
-        <v>50</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="7">
@@ -574,7 +574,7 @@
         <v>0.01</v>
       </c>
       <c r="C7">
-        <v>0.01</v>
+        <v>0.1</v>
       </c>
       <c r="D7">
         <v>1000</v>
@@ -586,16 +586,16 @@
         <v>0.05</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>0.1162790697674419</v>
       </c>
       <c r="H7">
-        <v>1</v>
+        <v>0.8837209302325582</v>
       </c>
       <c r="I7">
-        <v>0.9399999999999999</v>
+        <v>0.957</v>
       </c>
       <c r="J7">
-        <v>50</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="8">
@@ -606,7 +606,7 @@
         <v>0.01</v>
       </c>
       <c r="C8">
-        <v>0.01</v>
+        <v>0.1</v>
       </c>
       <c r="D8">
         <v>1000</v>
@@ -618,16 +618,16 @@
         <v>0.05</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>0.07692307692307693</v>
       </c>
       <c r="H8">
-        <v>1</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="I8">
-        <v>0.98</v>
+        <v>0.961</v>
       </c>
       <c r="J8">
-        <v>50</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="9">
@@ -638,7 +638,7 @@
         <v>0.01</v>
       </c>
       <c r="C9">
-        <v>0.01</v>
+        <v>0.1</v>
       </c>
       <c r="D9">
         <v>1000</v>
@@ -650,16 +650,16 @@
         <v>0.05</v>
       </c>
       <c r="G9">
-        <v>0.5</v>
+        <v>0.1568627450980392</v>
       </c>
       <c r="H9">
-        <v>0.5</v>
+        <v>0.8431372549019608</v>
       </c>
       <c r="I9">
-        <v>0.96</v>
+        <v>0.949</v>
       </c>
       <c r="J9">
-        <v>50</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="10">
@@ -682,16 +682,16 @@
         <v>0.05</v>
       </c>
       <c r="G10">
-        <v>0.25</v>
+        <v>0.1403508771929824</v>
       </c>
       <c r="H10">
-        <v>0.75</v>
+        <v>0.8596491228070176</v>
       </c>
       <c r="I10">
-        <v>0.92</v>
+        <v>0.9429999999999999</v>
       </c>
       <c r="J10">
-        <v>50</v>
+        <v>1000</v>
       </c>
     </row>
   </sheetData>
